--- a/AAII_Financials/Quarterly/ICAGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ICAGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="92">
   <si>
     <t>ICAGY</t>
   </si>
@@ -656,78 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45473</v>
       </c>
       <c r="J7" s="2">
         <v>45291</v>
       </c>
       <c r="K7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -770,8 +772,11 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -814,8 +819,11 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -858,8 +866,11 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +887,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,8 +932,11 @@
       <c r="P12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,8 +979,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1008,8 +1026,11 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1052,8 +1073,11 @@
       <c r="P15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,8 +1091,9 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1111,8 +1136,11 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1155,8 +1183,11 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1173,8 +1204,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1217,8 +1249,11 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1261,8 +1296,11 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1305,8 +1343,11 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1349,8 +1390,11 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1393,8 +1437,11 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1437,8 +1484,11 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1481,8 +1531,11 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1525,8 +1578,11 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1569,8 +1625,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1672,11 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1657,8 +1719,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1701,8 +1766,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1745,8 +1813,11 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1789,8 +1860,11 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1833,8 +1907,11 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1877,57 +1954,63 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45473</v>
       </c>
       <c r="J38" s="2">
         <v>45291</v>
       </c>
       <c r="K38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1944,8 +2027,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1962,404 +2046,432 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9993100</v>
+      </c>
+      <c r="E41" s="3">
         <v>8713200</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F41" s="3">
-        <v>9069900</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="F41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" s="3">
         <v>8478100</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I41" s="3">
-        <v>8266400</v>
+      <c r="I41" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J41" s="3">
         <v>6014100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="K41" s="3">
         <v>6014100</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M41" s="3">
+        <v>6014100</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O41" s="3">
         <v>11711800</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q41" s="3">
         <v>9827900</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>489000</v>
+      </c>
+      <c r="E42" s="3">
         <v>1020300</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
-        <v>1908400</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>1666800</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
-        <v>2124700</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>1508800</v>
       </c>
       <c r="K42" s="3">
-        <v>0</v>
+        <v>1508800</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>1508800</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>1399600</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>395400</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2129600</v>
+      </c>
+      <c r="E43" s="3">
         <v>3102000</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F43" s="3">
-        <v>2304200</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
         <v>3241500</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I43" s="3">
-        <v>2411900</v>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J43" s="3">
         <v>2809800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="K43" s="3">
         <v>2809800</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M43" s="3">
+        <v>2809800</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O43" s="3">
         <v>1937800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="3">
         <v>2125700</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>763200</v>
+      </c>
+      <c r="E44" s="3">
         <v>820700</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="3">
-        <v>739900</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
         <v>638800</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I44" s="3">
-        <v>630000</v>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J44" s="3">
         <v>546000</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="K44" s="3">
         <v>546000</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M44" s="3">
+        <v>546000</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O44" s="3">
         <v>445400</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q44" s="3">
         <v>377300</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3934700</v>
+      </c>
+      <c r="E45" s="3">
         <v>463800</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2926600</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3">
         <v>748500</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2381900</v>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J45" s="3">
         <v>362600</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="K45" s="3">
         <v>362600</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
+        <v>362600</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O45" s="3">
         <v>1798000</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>709600</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17309500</v>
+      </c>
+      <c r="E46" s="3">
         <v>15270600</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46" s="3">
-        <v>16948900</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="F46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" s="3">
         <v>15722100</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I46" s="3">
-        <v>15814900</v>
+      <c r="I46" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J46" s="3">
         <v>12104600</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L46" s="3">
+      <c r="K46" s="3">
         <v>12104600</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M46" s="3">
+        <v>12104600</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O46" s="3">
         <v>17292600</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q46" s="3">
         <v>14154100</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>425000</v>
+      </c>
+      <c r="E47" s="3">
         <v>398000</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F47" s="3">
-        <v>333500</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3">
         <v>242300</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I47" s="3">
-        <v>241100</v>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J47" s="3">
         <v>259800</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="K47" s="3">
         <v>259800</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M47" s="3">
+        <v>259800</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O47" s="3">
         <v>173600</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q47" s="3">
         <v>104700</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25085100</v>
+      </c>
+      <c r="E48" s="3">
         <v>25179100</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="3">
-        <v>25053400</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="F48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" s="3">
         <v>21878000</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I48" s="3">
-        <v>21935100</v>
+      <c r="I48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J48" s="3">
         <v>21859200</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="K48" s="3">
         <v>21859200</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M48" s="3">
+        <v>21859200</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O48" s="3">
         <v>20663800</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="3">
         <v>19606700</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4456800</v>
+      </c>
+      <c r="E49" s="3">
         <v>4426400</v>
       </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
       <c r="F49" s="3">
-        <v>4323000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
         <v>3770600</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
-        <v>3722300</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>3683000</v>
       </c>
       <c r="K49" s="3">
-        <v>0</v>
+        <v>3683000</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>3683000</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
         <v>4101500</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
       <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
         <v>3800400</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2402,8 +2514,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2446,52 +2561,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4725200</v>
+      </c>
+      <c r="E52" s="3">
         <v>4233900</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F52" s="3">
-        <v>4059900</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H52" s="3">
         <v>2946500</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I52" s="3">
-        <v>2881200</v>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J52" s="3">
         <v>2404100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="K52" s="3">
+        <v>2404100</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M52" s="3">
         <v>2414100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N52" s="3">
+      <c r="N52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O52" s="3">
         <v>2635400</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="3">
         <v>2967800</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2534,52 +2655,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>52682500</v>
+      </c>
+      <c r="E54" s="3">
         <v>50310000</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F54" s="3">
-        <v>51662900</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="F54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H54" s="3">
         <v>45350500</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I54" s="3">
-        <v>45493400</v>
+      <c r="I54" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J54" s="3">
         <v>41649200</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="K54" s="3">
         <v>41649200</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M54" s="3">
+        <v>41649200</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O54" s="3">
         <v>46425800</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q54" s="3">
         <v>42003800</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2596,8 +2723,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2614,272 +2742,291 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6933600</v>
+      </c>
+      <c r="E57" s="3">
         <v>3410800</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F57" s="3">
-        <v>7417500</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H57" s="3">
         <v>3468300</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3">
-        <v>6729900</v>
+      <c r="I57" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J57" s="3">
         <v>3511700</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="K57" s="3">
         <v>3511700</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M57" s="3">
+        <v>3511700</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O57" s="3">
         <v>6346100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q57" s="3">
         <v>3173000</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2202700</v>
+      </c>
+      <c r="E58" s="3">
         <v>3576400</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
-        <v>3433900</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>3597700</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
-        <v>3426600</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>3290600</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>3290600</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>3290600</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>3645200</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>3038400</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13285700</v>
+      </c>
+      <c r="E59" s="3">
         <v>13340400</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3">
-        <v>13903700</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3">
         <v>11811800</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I59" s="3">
-        <v>12275800</v>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J59" s="3">
         <v>11723200</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="K59" s="3">
         <v>11723200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
+        <v>11723200</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O59" s="3">
         <v>12555700</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q59" s="3">
         <v>10640200</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22523700</v>
+      </c>
+      <c r="E60" s="3">
         <v>21777600</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F60" s="3">
-        <v>24839700</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" s="3">
         <v>20044500</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I60" s="3">
-        <v>22501900</v>
+      <c r="I60" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J60" s="3">
         <v>19570000</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="K60" s="3">
         <v>19570000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M60" s="3">
+        <v>19570000</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O60" s="3">
         <v>22614600</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q60" s="3">
         <v>17805900</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13639900</v>
+      </c>
+      <c r="E61" s="3">
         <v>13174800</v>
       </c>
-      <c r="E61" s="3">
-        <v>0</v>
-      </c>
       <c r="F61" s="3">
-        <v>13955400</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>14359700</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
-        <v>13840100</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>14485500</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>14485500</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>14485500</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>17777300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>18318900</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4559600</v>
+      </c>
+      <c r="E62" s="3">
         <v>4704700</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="3">
-        <v>5112200</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3">
         <v>3939300</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3601200</v>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J62" s="3">
         <v>3488400</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="K62" s="3">
         <v>3488400</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
+        <v>3488400</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
         <v>3217200</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3">
         <v>3137800</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2922,8 +3069,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2966,8 +3116,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3010,52 +3163,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>42821900</v>
+      </c>
+      <c r="E66" s="3">
         <v>41393700</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F66" s="3">
-        <v>44664700</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="F66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3">
         <v>38956400</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I66" s="3">
-        <v>40380400</v>
+      <c r="I66" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J66" s="3">
         <v>38025900</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="K66" s="3">
         <v>38025900</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M66" s="3">
+        <v>38025900</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O66" s="3">
         <v>44158300</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q66" s="3">
         <v>39842900</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3072,8 +3231,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3116,8 +3276,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3160,8 +3323,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3204,8 +3370,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3248,25 +3417,28 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="3">
         <v>3517700</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="F72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
         <v>-126300</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>4</v>
@@ -3274,14 +3446,14 @@
       <c r="J72" s="3">
         <v>-3204400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="K72" s="3">
         <v>-3204400</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>4</v>
+      <c r="L72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M72" s="3">
+        <v>-3204400</v>
       </c>
       <c r="N72" s="3" t="s">
         <v>4</v>
@@ -3289,11 +3461,14 @@
       <c r="O72" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-4815600</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3336,8 +3511,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +3558,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3424,52 +3605,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9853800</v>
+      </c>
+      <c r="E76" s="3">
         <v>8909200</v>
       </c>
-      <c r="E76" s="3">
-        <v>6984600</v>
-      </c>
-      <c r="F76" s="3">
-        <v>6991200</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="F76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" s="3">
         <v>6387800</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I76" s="3">
-        <v>5106600</v>
+      <c r="I76" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J76" s="3">
         <v>3616700</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="K76" s="3">
         <v>3616700</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M76" s="3">
+        <v>3616700</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O76" s="3">
         <v>2260900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2190400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2154500</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3512,57 +3699,63 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45473</v>
       </c>
       <c r="J80" s="2">
         <v>45291</v>
       </c>
       <c r="K80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3605,8 +3798,11 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3623,8 +3819,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3667,8 +3864,11 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3711,8 +3911,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3755,8 +3958,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3799,8 +4005,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3843,8 +4052,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3887,8 +4099,11 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3931,8 +4146,11 @@
       <c r="P89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3949,8 +4167,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3993,8 +4212,11 @@
       <c r="P91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4037,8 +4259,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4081,8 +4306,11 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4125,8 +4353,11 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4143,8 +4374,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4187,8 +4419,11 @@
       <c r="P96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4231,8 +4466,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4275,8 +4513,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4319,8 +4560,11 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4363,8 +4607,11 @@
       <c r="P100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4407,8 +4654,11 @@
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4449,6 +4699,9 @@
         <v>4</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
